--- a/input/mapping/004. OCB_GOLD_TCKH_V_CDTK_DAILY_QUANG.xlsx
+++ b/input/mapping/004. OCB_GOLD_TCKH_V_CDTK_DAILY_QUANG.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/01.REVIEWED__OK/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{099671D1-19F9-4520-813A-44AF8C243A0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BC1F556-95D4-4E2E-904C-BB65486EEDCE}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="8_{099671D1-19F9-4520-813A-44AF8C243A0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6000B834-6BCB-4F4D-A105-89A55342F818}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -185,8 +185,8 @@
     DSC,
     DCN,
     DCC,
-    `Table Names`,
-    `File Paths`,
+    Table_Names,
+    File_Paths,
     DATA_DAY,
     DATA_MONTH,
     DATA_YEAR,
@@ -264,9 +264,14 @@
 ) ON [PRIMARY]</t>
   </si>
   <si>
-    <t>USE CATALOG IDENTIFIER(:curated);
+    <t xml:space="preserve">USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
-CREATE OR REPLACE TABLE holiday AS
+INSERT OVERWRITE holiday (
+    DATA_DATE_DT,
+    HOLIDAY_DATE_DT,
+    DATA_DT,
+    HOLIDAY_DT
+)
 SELECT
     TO_DATE(CAST(MAX(W.msr_prd_id) AS STRING), 'yyyyMMdd')   AS DATA_DATE_DT,
     TO_DATE(CAST(D.msr_prd_id AS STRING), 'yyyyMMdd')        AS HOLIDAY_DATE_DT,
@@ -277,12 +282,21 @@
     ON  D.msr_prd_id &gt; W.msr_prd_id
     AND W.bsn_day_f = 1
 WHERE D.bsn_day_f = 0
-GROUP BY D.msr_prd_id;</t>
+GROUP BY D.msr_prd_id;
+</t>
   </si>
   <si>
     <t xml:space="preserve">USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
-CREATE OR REPLACE TABLE working_day AS
+INSERT OVERWRITE working_day (
+    DATA_DT,
+    FROM_DATE_DT,
+    FROM_DT,
+    END_DT,
+    END_DATE_DT,
+    BEGIN_OF_MONTH,
+    BEGIN_OF_MONTH_DATE
+)
 WITH
 v_from_dt AS (
     SELECT
@@ -1424,13 +1438,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2165,7 +2179,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="180.75">
+    <row r="8" spans="1:3" ht="252.75">
       <c r="A8" s="25" t="s">
         <v>25</v>
       </c>
@@ -2206,7 +2220,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="65" t="s">
         <v>35</v>
       </c>
       <c r="B1" s="83"/>
@@ -2216,7 +2230,7 @@
       <c r="F1" s="83"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="65" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="83"/>
@@ -2280,7 +2294,7 @@
       <c r="F5" s="2"/>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1">
-      <c r="A7" s="67" t="s">
+      <c r="A7" s="65" t="s">
         <v>49</v>
       </c>
       <c r="B7" s="83"/>
@@ -2296,10 +2310,10 @@
       <c r="B8" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="65" t="s">
+      <c r="C8" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="66"/>
+      <c r="D8" s="67"/>
       <c r="E8" s="27" t="s">
         <v>53</v>
       </c>
@@ -2620,22 +2634,22 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
